--- a/wwwroot/ExcelModel/Adidas_FLAM_sheet.xlsx
+++ b/wwwroot/ExcelModel/Adidas_FLAM_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\ReviewCommandSystem\Content\assets\ExcelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D914EF50-1289-4026-8C15-F782E2A18BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3814843E-C1C0-4A83-81CA-BC209886547D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="2614" windowWidth="24686" windowHeight="13132" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXEMPT" sheetId="21" r:id="rId1"/>
@@ -923,56 +923,38 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -996,13 +978,31 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1280,15 +1280,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626CC06E-9590-4323-BE24-60512668D6F0}">
   <dimension ref="A1:AM50"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="7" width="2.33203125" customWidth="1"/>
+    <col min="1" max="7" width="2.35546875" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.109375" customWidth="1"/>
-    <col min="32" max="39" width="2.33203125" customWidth="1"/>
+    <col min="9" max="31" width="2.140625" customWidth="1"/>
+    <col min="32" max="39" width="2.35546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1328,7 +1328,7 @@
       <c r="AL1" s="39"/>
       <c r="AM1" s="15"/>
     </row>
-    <row r="2" spans="1:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
@@ -1361,7 +1361,7 @@
       <c r="AE2" s="1"/>
       <c r="AF2" s="1"/>
     </row>
-    <row r="3" spans="1:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="40" t="s">
         <v>5</v>
       </c>
@@ -1397,7 +1397,7 @@
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
     </row>
-    <row r="4" spans="1:39" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -1428,7 +1428,7 @@
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
     </row>
-    <row r="5" spans="1:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
         <v>6</v>
       </c>
@@ -1464,7 +1464,7 @@
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
     </row>
-    <row r="6" spans="1:39" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1498,12 +1498,12 @@
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
         <v>1</v>
       </c>
@@ -1511,10 +1511,10 @@
       <c r="E9" s="37"/>
       <c r="F9" s="37"/>
     </row>
-    <row r="10" spans="1:39" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" ht="15.45" x14ac:dyDescent="0.35">
       <c r="A10" s="23"/>
     </row>
-    <row r="11" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:39" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" ht="15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D14" t="s">
         <v>29</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
         <v>1</v>
       </c>
@@ -1582,10 +1582,10 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" ht="15.45" x14ac:dyDescent="0.35">
       <c r="A17" s="23"/>
     </row>
-    <row r="18" spans="1:32" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" ht="15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
         <v>29</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
         <v>1</v>
       </c>
@@ -1653,10 +1653,10 @@
       <c r="E23" s="37"/>
       <c r="F23" s="37"/>
     </row>
-    <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" ht="15.45" x14ac:dyDescent="0.35">
       <c r="A24" s="23"/>
     </row>
-    <row r="25" spans="1:32" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" ht="15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D28" t="s">
         <v>29</v>
       </c>
@@ -1716,12 +1716,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" ht="15" x14ac:dyDescent="0.35">
       <c r="A31" s="27" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="21" t="s">
         <v>1</v>
       </c>
@@ -1729,7 +1729,7 @@
       <c r="E33" s="37"/>
       <c r="F33" s="37"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="33" t="s">
         <v>75</v>
       </c>
@@ -1737,12 +1737,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="34" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>29</v>
       </c>
@@ -1750,10 +1750,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B39" s="21"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -1761,43 +1761,43 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="28" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="28"/>
       <c r="D47" s="28" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="28" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="35" t="s">
         <v>22</v>
       </c>
@@ -1832,15 +1832,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F9B524C-DB95-4CE7-88C8-094F5D105146}">
   <dimension ref="A1:AM70"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="7" width="2.33203125" customWidth="1"/>
+    <col min="1" max="7" width="2.35546875" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.109375" customWidth="1"/>
-    <col min="32" max="39" width="2.33203125" customWidth="1"/>
+    <col min="9" max="31" width="2.140625" customWidth="1"/>
+    <col min="32" max="39" width="2.35546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1880,7 +1880,7 @@
       <c r="AL1" s="39"/>
       <c r="AM1" s="15"/>
     </row>
-    <row r="2" spans="1:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
@@ -1913,7 +1913,7 @@
       <c r="AE2" s="1"/>
       <c r="AF2" s="1"/>
     </row>
-    <row r="3" spans="1:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="40" t="s">
         <v>5</v>
       </c>
@@ -1949,91 +1949,91 @@
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
     </row>
-    <row r="4" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
+    <row r="4" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
-      <c r="V4" s="69"/>
-      <c r="W4" s="69"/>
-      <c r="X4" s="69"/>
-      <c r="Y4" s="69"/>
-      <c r="Z4" s="69"/>
-      <c r="AA4" s="69"/>
-      <c r="AB4" s="69"/>
-      <c r="AC4" s="69"/>
-      <c r="AD4" s="69"/>
-      <c r="AE4" s="69"/>
-      <c r="AF4" s="69"/>
-      <c r="AG4" s="69"/>
-      <c r="AH4" s="69"/>
-      <c r="AI4" s="69"/>
-      <c r="AJ4" s="69"/>
-      <c r="AK4" s="69"/>
-      <c r="AL4" s="69"/>
-      <c r="AM4" s="69"/>
-    </row>
-    <row r="5" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="69"/>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="69"/>
-      <c r="R5" s="69"/>
-      <c r="S5" s="69"/>
-      <c r="T5" s="69"/>
-      <c r="U5" s="69"/>
-      <c r="V5" s="69"/>
-      <c r="W5" s="69"/>
-      <c r="X5" s="69"/>
-      <c r="Y5" s="69"/>
-      <c r="Z5" s="69"/>
-      <c r="AA5" s="69"/>
-      <c r="AB5" s="69"/>
-      <c r="AC5" s="69"/>
-      <c r="AD5" s="69"/>
-      <c r="AE5" s="69"/>
-      <c r="AF5" s="69"/>
-      <c r="AG5" s="69"/>
-      <c r="AH5" s="69"/>
-      <c r="AI5" s="69"/>
-      <c r="AJ5" s="69"/>
-      <c r="AK5" s="69"/>
-      <c r="AL5" s="69"/>
-      <c r="AM5" s="69"/>
-    </row>
-    <row r="6" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="62"/>
+      <c r="Y4" s="62"/>
+      <c r="Z4" s="62"/>
+      <c r="AA4" s="62"/>
+      <c r="AB4" s="62"/>
+      <c r="AC4" s="62"/>
+      <c r="AD4" s="62"/>
+      <c r="AE4" s="62"/>
+      <c r="AF4" s="62"/>
+      <c r="AG4" s="62"/>
+      <c r="AH4" s="62"/>
+      <c r="AI4" s="62"/>
+      <c r="AJ4" s="62"/>
+      <c r="AK4" s="62"/>
+      <c r="AL4" s="62"/>
+      <c r="AM4" s="72"/>
+    </row>
+    <row r="5" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="62"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="62"/>
+      <c r="Z5" s="62"/>
+      <c r="AA5" s="62"/>
+      <c r="AB5" s="62"/>
+      <c r="AC5" s="62"/>
+      <c r="AD5" s="62"/>
+      <c r="AE5" s="62"/>
+      <c r="AF5" s="62"/>
+      <c r="AG5" s="62"/>
+      <c r="AH5" s="62"/>
+      <c r="AI5" s="62"/>
+      <c r="AJ5" s="62"/>
+      <c r="AK5" s="62"/>
+      <c r="AL5" s="62"/>
+      <c r="AM5" s="72"/>
+    </row>
+    <row r="6" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
         <v>1</v>
       </c>
@@ -2074,7 +2074,7 @@
       <c r="AL6" s="16"/>
       <c r="AM6" s="15"/>
     </row>
-    <row r="7" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
         <v>30</v>
       </c>
@@ -2119,7 +2119,7 @@
       <c r="AL7" s="16"/>
       <c r="AM7" s="15"/>
     </row>
-    <row r="8" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="29"/>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
@@ -2161,7 +2161,7 @@
       <c r="AL8" s="16"/>
       <c r="AM8" s="15"/>
     </row>
-    <row r="9" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2201,7 +2201,7 @@
       <c r="AL9" s="16"/>
       <c r="AM9" s="15"/>
     </row>
-    <row r="10" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
         <v>33</v>
       </c>
@@ -2246,7 +2246,7 @@
       <c r="AL10" s="16"/>
       <c r="AM10" s="15"/>
     </row>
-    <row r="11" spans="1:39" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:39" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>36</v>
       </c>
@@ -2286,1228 +2286,1228 @@
       <c r="AL11" s="16"/>
       <c r="AM11" s="15"/>
     </row>
-    <row r="12" spans="1:39" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="70" t="s">
+    <row r="12" spans="1:39" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="72"/>
-      <c r="T12" s="70" t="s">
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="64"/>
+      <c r="R12" s="64"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="U12" s="71"/>
-      <c r="V12" s="71"/>
-      <c r="W12" s="71"/>
-      <c r="X12" s="71"/>
-      <c r="Y12" s="71"/>
-      <c r="Z12" s="71"/>
-      <c r="AA12" s="71"/>
-      <c r="AB12" s="71"/>
-      <c r="AC12" s="71"/>
-      <c r="AD12" s="71"/>
-      <c r="AE12" s="71"/>
-      <c r="AF12" s="71"/>
-      <c r="AG12" s="71"/>
-      <c r="AH12" s="71"/>
-      <c r="AI12" s="71"/>
-      <c r="AJ12" s="71"/>
-      <c r="AK12" s="71"/>
-      <c r="AL12" s="72"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="64"/>
+      <c r="W12" s="64"/>
+      <c r="X12" s="64"/>
+      <c r="Y12" s="64"/>
+      <c r="Z12" s="64"/>
+      <c r="AA12" s="64"/>
+      <c r="AB12" s="64"/>
+      <c r="AC12" s="64"/>
+      <c r="AD12" s="64"/>
+      <c r="AE12" s="64"/>
+      <c r="AF12" s="64"/>
+      <c r="AG12" s="64"/>
+      <c r="AH12" s="64"/>
+      <c r="AI12" s="64"/>
+      <c r="AJ12" s="64"/>
+      <c r="AK12" s="64"/>
+      <c r="AL12" s="65"/>
       <c r="AM12" s="15"/>
     </row>
-    <row r="13" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="61" t="s">
+    <row r="13" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
-      <c r="L13" s="62"/>
-      <c r="M13" s="62"/>
-      <c r="N13" s="62"/>
-      <c r="O13" s="62"/>
-      <c r="P13" s="62"/>
-      <c r="Q13" s="62"/>
-      <c r="R13" s="62"/>
-      <c r="S13" s="63"/>
-      <c r="T13" s="61" t="s">
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="56"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="U13" s="62"/>
-      <c r="V13" s="62"/>
-      <c r="W13" s="62"/>
-      <c r="X13" s="62"/>
-      <c r="Y13" s="62"/>
-      <c r="Z13" s="62"/>
-      <c r="AA13" s="62"/>
-      <c r="AB13" s="62"/>
-      <c r="AC13" s="62"/>
-      <c r="AD13" s="62"/>
-      <c r="AE13" s="62"/>
-      <c r="AF13" s="62"/>
-      <c r="AG13" s="62"/>
-      <c r="AH13" s="62"/>
-      <c r="AI13" s="62"/>
-      <c r="AJ13" s="62"/>
-      <c r="AK13" s="62"/>
-      <c r="AL13" s="63"/>
+      <c r="U13" s="56"/>
+      <c r="V13" s="56"/>
+      <c r="W13" s="56"/>
+      <c r="X13" s="56"/>
+      <c r="Y13" s="56"/>
+      <c r="Z13" s="56"/>
+      <c r="AA13" s="56"/>
+      <c r="AB13" s="56"/>
+      <c r="AC13" s="56"/>
+      <c r="AD13" s="56"/>
+      <c r="AE13" s="56"/>
+      <c r="AF13" s="56"/>
+      <c r="AG13" s="56"/>
+      <c r="AH13" s="56"/>
+      <c r="AI13" s="56"/>
+      <c r="AJ13" s="56"/>
+      <c r="AK13" s="56"/>
+      <c r="AL13" s="57"/>
       <c r="AM13" s="15"/>
     </row>
-    <row r="14" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="61"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="62"/>
-      <c r="S14" s="63"/>
-      <c r="T14" s="61"/>
-      <c r="U14" s="62"/>
-      <c r="V14" s="62"/>
-      <c r="W14" s="62"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="62"/>
-      <c r="Z14" s="62"/>
-      <c r="AA14" s="62"/>
-      <c r="AB14" s="62"/>
-      <c r="AC14" s="62"/>
-      <c r="AD14" s="62"/>
-      <c r="AE14" s="62"/>
-      <c r="AF14" s="62"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62"/>
-      <c r="AI14" s="62"/>
-      <c r="AJ14" s="62"/>
-      <c r="AK14" s="62"/>
-      <c r="AL14" s="63"/>
+    <row r="14" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="55"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="56"/>
+      <c r="N14" s="56"/>
+      <c r="O14" s="56"/>
+      <c r="P14" s="56"/>
+      <c r="Q14" s="56"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="55"/>
+      <c r="U14" s="56"/>
+      <c r="V14" s="56"/>
+      <c r="W14" s="56"/>
+      <c r="X14" s="56"/>
+      <c r="Y14" s="56"/>
+      <c r="Z14" s="56"/>
+      <c r="AA14" s="56"/>
+      <c r="AB14" s="56"/>
+      <c r="AC14" s="56"/>
+      <c r="AD14" s="56"/>
+      <c r="AE14" s="56"/>
+      <c r="AF14" s="56"/>
+      <c r="AG14" s="56"/>
+      <c r="AH14" s="56"/>
+      <c r="AI14" s="56"/>
+      <c r="AJ14" s="56"/>
+      <c r="AK14" s="56"/>
+      <c r="AL14" s="57"/>
       <c r="AM14" s="15"/>
     </row>
-    <row r="15" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="61"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="62"/>
-      <c r="L15" s="62"/>
-      <c r="M15" s="62"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62"/>
-      <c r="S15" s="63"/>
-      <c r="T15" s="61"/>
-      <c r="U15" s="62"/>
-      <c r="V15" s="62"/>
-      <c r="W15" s="62"/>
-      <c r="X15" s="62"/>
-      <c r="Y15" s="62"/>
-      <c r="Z15" s="62"/>
-      <c r="AA15" s="62"/>
-      <c r="AB15" s="62"/>
-      <c r="AC15" s="62"/>
-      <c r="AD15" s="62"/>
-      <c r="AE15" s="62"/>
-      <c r="AF15" s="62"/>
-      <c r="AG15" s="62"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="62"/>
-      <c r="AJ15" s="62"/>
-      <c r="AK15" s="62"/>
-      <c r="AL15" s="63"/>
+    <row r="15" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="55"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="56"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="56"/>
+      <c r="P15" s="56"/>
+      <c r="Q15" s="56"/>
+      <c r="R15" s="56"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="55"/>
+      <c r="U15" s="56"/>
+      <c r="V15" s="56"/>
+      <c r="W15" s="56"/>
+      <c r="X15" s="56"/>
+      <c r="Y15" s="56"/>
+      <c r="Z15" s="56"/>
+      <c r="AA15" s="56"/>
+      <c r="AB15" s="56"/>
+      <c r="AC15" s="56"/>
+      <c r="AD15" s="56"/>
+      <c r="AE15" s="56"/>
+      <c r="AF15" s="56"/>
+      <c r="AG15" s="56"/>
+      <c r="AH15" s="56"/>
+      <c r="AI15" s="56"/>
+      <c r="AJ15" s="56"/>
+      <c r="AK15" s="56"/>
+      <c r="AL15" s="57"/>
       <c r="AM15" s="15"/>
     </row>
-    <row r="16" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="61"/>
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="62"/>
-      <c r="L16" s="62"/>
-      <c r="M16" s="62"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="62"/>
-      <c r="P16" s="62"/>
-      <c r="Q16" s="62"/>
-      <c r="R16" s="62"/>
-      <c r="S16" s="63"/>
-      <c r="T16" s="61"/>
-      <c r="U16" s="62"/>
-      <c r="V16" s="62"/>
-      <c r="W16" s="62"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="62"/>
-      <c r="Z16" s="62"/>
-      <c r="AA16" s="62"/>
-      <c r="AB16" s="62"/>
-      <c r="AC16" s="62"/>
-      <c r="AD16" s="62"/>
-      <c r="AE16" s="62"/>
-      <c r="AF16" s="62"/>
-      <c r="AG16" s="62"/>
-      <c r="AH16" s="62"/>
-      <c r="AI16" s="62"/>
-      <c r="AJ16" s="62"/>
-      <c r="AK16" s="62"/>
-      <c r="AL16" s="63"/>
+    <row r="16" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="55"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="56"/>
+      <c r="P16" s="56"/>
+      <c r="Q16" s="56"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="55"/>
+      <c r="U16" s="56"/>
+      <c r="V16" s="56"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="56"/>
+      <c r="Y16" s="56"/>
+      <c r="Z16" s="56"/>
+      <c r="AA16" s="56"/>
+      <c r="AB16" s="56"/>
+      <c r="AC16" s="56"/>
+      <c r="AD16" s="56"/>
+      <c r="AE16" s="56"/>
+      <c r="AF16" s="56"/>
+      <c r="AG16" s="56"/>
+      <c r="AH16" s="56"/>
+      <c r="AI16" s="56"/>
+      <c r="AJ16" s="56"/>
+      <c r="AK16" s="56"/>
+      <c r="AL16" s="57"/>
       <c r="AM16" s="15"/>
     </row>
-    <row r="17" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="64" t="s">
+    <row r="17" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="65"/>
-      <c r="K17" s="65"/>
-      <c r="L17" s="66" t="s">
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="59"/>
+      <c r="L17" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="M17" s="66"/>
-      <c r="N17" s="66"/>
-      <c r="O17" s="66"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="67"/>
-      <c r="T17" s="64" t="s">
+      <c r="M17" s="60"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="60"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="61"/>
+      <c r="T17" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="U17" s="65"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="65"/>
-      <c r="X17" s="65"/>
-      <c r="Y17" s="65"/>
-      <c r="Z17" s="65"/>
-      <c r="AA17" s="65"/>
-      <c r="AB17" s="65"/>
-      <c r="AC17" s="65"/>
-      <c r="AD17" s="65"/>
-      <c r="AE17" s="66" t="s">
+      <c r="U17" s="59"/>
+      <c r="V17" s="59"/>
+      <c r="W17" s="59"/>
+      <c r="X17" s="59"/>
+      <c r="Y17" s="59"/>
+      <c r="Z17" s="59"/>
+      <c r="AA17" s="59"/>
+      <c r="AB17" s="59"/>
+      <c r="AC17" s="59"/>
+      <c r="AD17" s="59"/>
+      <c r="AE17" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="AF17" s="66"/>
-      <c r="AG17" s="66"/>
-      <c r="AH17" s="66"/>
-      <c r="AI17" s="66"/>
-      <c r="AJ17" s="66"/>
-      <c r="AK17" s="66"/>
-      <c r="AL17" s="67"/>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="61"/>
       <c r="AM17" s="15"/>
     </row>
-    <row r="18" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="64"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="65"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="66"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="66"/>
-      <c r="O18" s="66"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="66"/>
-      <c r="S18" s="67"/>
-      <c r="T18" s="64"/>
-      <c r="U18" s="65"/>
-      <c r="V18" s="65"/>
-      <c r="W18" s="65"/>
-      <c r="X18" s="65"/>
-      <c r="Y18" s="65"/>
-      <c r="Z18" s="65"/>
-      <c r="AA18" s="65"/>
-      <c r="AB18" s="65"/>
-      <c r="AC18" s="65"/>
-      <c r="AD18" s="65"/>
-      <c r="AE18" s="66"/>
-      <c r="AF18" s="66"/>
-      <c r="AG18" s="66"/>
-      <c r="AH18" s="66"/>
-      <c r="AI18" s="66"/>
-      <c r="AJ18" s="66"/>
-      <c r="AK18" s="66"/>
-      <c r="AL18" s="67"/>
+    <row r="18" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="58"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="59"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="60"/>
+      <c r="Q18" s="60"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="61"/>
+      <c r="T18" s="58"/>
+      <c r="U18" s="59"/>
+      <c r="V18" s="59"/>
+      <c r="W18" s="59"/>
+      <c r="X18" s="59"/>
+      <c r="Y18" s="59"/>
+      <c r="Z18" s="59"/>
+      <c r="AA18" s="59"/>
+      <c r="AB18" s="59"/>
+      <c r="AC18" s="59"/>
+      <c r="AD18" s="59"/>
+      <c r="AE18" s="60"/>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="61"/>
       <c r="AM18" s="15"/>
     </row>
-    <row r="19" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="64"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="67"/>
-      <c r="T19" s="64"/>
-      <c r="U19" s="65"/>
-      <c r="V19" s="65"/>
-      <c r="W19" s="65"/>
-      <c r="X19" s="65"/>
-      <c r="Y19" s="65"/>
-      <c r="Z19" s="65"/>
-      <c r="AA19" s="65"/>
-      <c r="AB19" s="65"/>
-      <c r="AC19" s="65"/>
-      <c r="AD19" s="65"/>
-      <c r="AE19" s="66"/>
-      <c r="AF19" s="66"/>
-      <c r="AG19" s="66"/>
-      <c r="AH19" s="66"/>
-      <c r="AI19" s="66"/>
-      <c r="AJ19" s="66"/>
-      <c r="AK19" s="66"/>
-      <c r="AL19" s="67"/>
+    <row r="19" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="58"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="60"/>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="61"/>
+      <c r="T19" s="58"/>
+      <c r="U19" s="59"/>
+      <c r="V19" s="59"/>
+      <c r="W19" s="59"/>
+      <c r="X19" s="59"/>
+      <c r="Y19" s="59"/>
+      <c r="Z19" s="59"/>
+      <c r="AA19" s="59"/>
+      <c r="AB19" s="59"/>
+      <c r="AC19" s="59"/>
+      <c r="AD19" s="59"/>
+      <c r="AE19" s="60"/>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="61"/>
       <c r="AM19" s="15"/>
     </row>
-    <row r="20" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="59" t="s">
+    <row r="20" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="44" t="s">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="49"/>
+      <c r="L20" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="44"/>
-      <c r="S20" s="45"/>
-      <c r="T20" s="59" t="s">
+      <c r="M20" s="50"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="50"/>
+      <c r="S20" s="51"/>
+      <c r="T20" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="U20" s="60"/>
-      <c r="V20" s="60"/>
-      <c r="W20" s="60"/>
-      <c r="X20" s="60"/>
-      <c r="Y20" s="60"/>
-      <c r="Z20" s="60"/>
-      <c r="AA20" s="60"/>
-      <c r="AB20" s="60"/>
-      <c r="AC20" s="60"/>
-      <c r="AD20" s="60"/>
-      <c r="AE20" s="44" t="s">
+      <c r="U20" s="49"/>
+      <c r="V20" s="49"/>
+      <c r="W20" s="49"/>
+      <c r="X20" s="49"/>
+      <c r="Y20" s="49"/>
+      <c r="Z20" s="49"/>
+      <c r="AA20" s="49"/>
+      <c r="AB20" s="49"/>
+      <c r="AC20" s="49"/>
+      <c r="AD20" s="49"/>
+      <c r="AE20" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AF20" s="44"/>
-      <c r="AG20" s="44"/>
-      <c r="AH20" s="44"/>
-      <c r="AI20" s="44"/>
-      <c r="AJ20" s="44"/>
-      <c r="AK20" s="44"/>
-      <c r="AL20" s="45"/>
+      <c r="AF20" s="50"/>
+      <c r="AG20" s="50"/>
+      <c r="AH20" s="50"/>
+      <c r="AI20" s="50"/>
+      <c r="AJ20" s="50"/>
+      <c r="AK20" s="50"/>
+      <c r="AL20" s="51"/>
       <c r="AM20" s="15"/>
     </row>
-    <row r="21" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="59" t="s">
+    <row r="21" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="60"/>
-      <c r="L21" s="44" t="s">
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="44"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="59" t="s">
+      <c r="M21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="50"/>
+      <c r="Q21" s="50"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="U21" s="60"/>
-      <c r="V21" s="60"/>
-      <c r="W21" s="60"/>
-      <c r="X21" s="60"/>
-      <c r="Y21" s="60"/>
-      <c r="Z21" s="60"/>
-      <c r="AA21" s="60"/>
-      <c r="AB21" s="60"/>
-      <c r="AC21" s="60"/>
-      <c r="AD21" s="60"/>
-      <c r="AE21" s="44" t="s">
+      <c r="U21" s="49"/>
+      <c r="V21" s="49"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="49"/>
+      <c r="Y21" s="49"/>
+      <c r="Z21" s="49"/>
+      <c r="AA21" s="49"/>
+      <c r="AB21" s="49"/>
+      <c r="AC21" s="49"/>
+      <c r="AD21" s="49"/>
+      <c r="AE21" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="AF21" s="44"/>
-      <c r="AG21" s="44"/>
-      <c r="AH21" s="44"/>
-      <c r="AI21" s="44"/>
-      <c r="AJ21" s="44"/>
-      <c r="AK21" s="44"/>
-      <c r="AL21" s="45"/>
+      <c r="AF21" s="50"/>
+      <c r="AG21" s="50"/>
+      <c r="AH21" s="50"/>
+      <c r="AI21" s="50"/>
+      <c r="AJ21" s="50"/>
+      <c r="AK21" s="50"/>
+      <c r="AL21" s="51"/>
       <c r="AM21" s="15"/>
     </row>
-    <row r="22" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="59" t="s">
+    <row r="22" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="44" t="s">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="49"/>
+      <c r="L22" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="44"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="44"/>
-      <c r="R22" s="44"/>
-      <c r="S22" s="45"/>
-      <c r="T22" s="59" t="s">
+      <c r="M22" s="50"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="50"/>
+      <c r="P22" s="50"/>
+      <c r="Q22" s="50"/>
+      <c r="R22" s="50"/>
+      <c r="S22" s="51"/>
+      <c r="T22" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="U22" s="60"/>
-      <c r="V22" s="60"/>
-      <c r="W22" s="60"/>
-      <c r="X22" s="60"/>
-      <c r="Y22" s="60"/>
-      <c r="Z22" s="60"/>
-      <c r="AA22" s="60"/>
-      <c r="AB22" s="60"/>
-      <c r="AC22" s="60"/>
-      <c r="AD22" s="60"/>
-      <c r="AE22" s="44" t="s">
+      <c r="U22" s="49"/>
+      <c r="V22" s="49"/>
+      <c r="W22" s="49"/>
+      <c r="X22" s="49"/>
+      <c r="Y22" s="49"/>
+      <c r="Z22" s="49"/>
+      <c r="AA22" s="49"/>
+      <c r="AB22" s="49"/>
+      <c r="AC22" s="49"/>
+      <c r="AD22" s="49"/>
+      <c r="AE22" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="AF22" s="44"/>
-      <c r="AG22" s="44"/>
-      <c r="AH22" s="44"/>
-      <c r="AI22" s="44"/>
-      <c r="AJ22" s="44"/>
-      <c r="AK22" s="44"/>
-      <c r="AL22" s="45"/>
+      <c r="AF22" s="50"/>
+      <c r="AG22" s="50"/>
+      <c r="AH22" s="50"/>
+      <c r="AI22" s="50"/>
+      <c r="AJ22" s="50"/>
+      <c r="AK22" s="50"/>
+      <c r="AL22" s="51"/>
       <c r="AM22" s="15"/>
     </row>
-    <row r="23" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="59" t="s">
+    <row r="23" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="60"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="44" t="s">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="49"/>
+      <c r="L23" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="44"/>
-      <c r="R23" s="44"/>
-      <c r="S23" s="45"/>
-      <c r="T23" s="59" t="s">
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="50"/>
+      <c r="Q23" s="50"/>
+      <c r="R23" s="50"/>
+      <c r="S23" s="51"/>
+      <c r="T23" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="U23" s="60"/>
-      <c r="V23" s="60"/>
-      <c r="W23" s="60"/>
-      <c r="X23" s="60"/>
-      <c r="Y23" s="60"/>
-      <c r="Z23" s="60"/>
-      <c r="AA23" s="60"/>
-      <c r="AB23" s="60"/>
-      <c r="AC23" s="60"/>
-      <c r="AD23" s="60"/>
-      <c r="AE23" s="44" t="s">
+      <c r="U23" s="49"/>
+      <c r="V23" s="49"/>
+      <c r="W23" s="49"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="49"/>
+      <c r="Z23" s="49"/>
+      <c r="AA23" s="49"/>
+      <c r="AB23" s="49"/>
+      <c r="AC23" s="49"/>
+      <c r="AD23" s="49"/>
+      <c r="AE23" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="AF23" s="44"/>
-      <c r="AG23" s="44"/>
-      <c r="AH23" s="44"/>
-      <c r="AI23" s="44"/>
-      <c r="AJ23" s="44"/>
-      <c r="AK23" s="44"/>
-      <c r="AL23" s="45"/>
+      <c r="AF23" s="50"/>
+      <c r="AG23" s="50"/>
+      <c r="AH23" s="50"/>
+      <c r="AI23" s="50"/>
+      <c r="AJ23" s="50"/>
+      <c r="AK23" s="50"/>
+      <c r="AL23" s="51"/>
       <c r="AM23" s="15"/>
     </row>
-    <row r="24" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="59" t="s">
+    <row r="24" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="60"/>
-      <c r="C24" s="60"/>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="60"/>
-      <c r="J24" s="60"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="44" t="s">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="M24" s="44"/>
-      <c r="N24" s="44"/>
-      <c r="O24" s="44"/>
-      <c r="P24" s="44"/>
-      <c r="Q24" s="44"/>
-      <c r="R24" s="44"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="59" t="s">
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="50"/>
+      <c r="P24" s="50"/>
+      <c r="Q24" s="50"/>
+      <c r="R24" s="50"/>
+      <c r="S24" s="51"/>
+      <c r="T24" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="U24" s="60"/>
-      <c r="V24" s="60"/>
-      <c r="W24" s="60"/>
-      <c r="X24" s="60"/>
-      <c r="Y24" s="60"/>
-      <c r="Z24" s="60"/>
-      <c r="AA24" s="60"/>
-      <c r="AB24" s="60"/>
-      <c r="AC24" s="60"/>
-      <c r="AD24" s="60"/>
-      <c r="AE24" s="44" t="s">
+      <c r="U24" s="49"/>
+      <c r="V24" s="49"/>
+      <c r="W24" s="49"/>
+      <c r="X24" s="49"/>
+      <c r="Y24" s="49"/>
+      <c r="Z24" s="49"/>
+      <c r="AA24" s="49"/>
+      <c r="AB24" s="49"/>
+      <c r="AC24" s="49"/>
+      <c r="AD24" s="49"/>
+      <c r="AE24" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="AF24" s="44"/>
-      <c r="AG24" s="44"/>
-      <c r="AH24" s="44"/>
-      <c r="AI24" s="44"/>
-      <c r="AJ24" s="44"/>
-      <c r="AK24" s="44"/>
-      <c r="AL24" s="45"/>
+      <c r="AF24" s="50"/>
+      <c r="AG24" s="50"/>
+      <c r="AH24" s="50"/>
+      <c r="AI24" s="50"/>
+      <c r="AJ24" s="50"/>
+      <c r="AK24" s="50"/>
+      <c r="AL24" s="51"/>
       <c r="AM24" s="15"/>
     </row>
-    <row r="25" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
+    <row r="25" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="42"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="42"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="42"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="42"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="41" t="s">
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="53"/>
+      <c r="R25" s="53"/>
+      <c r="S25" s="54"/>
+      <c r="T25" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="U25" s="42"/>
-      <c r="V25" s="42"/>
-      <c r="W25" s="42"/>
-      <c r="X25" s="42"/>
-      <c r="Y25" s="42"/>
-      <c r="Z25" s="42"/>
-      <c r="AA25" s="42"/>
-      <c r="AB25" s="42"/>
-      <c r="AC25" s="42"/>
-      <c r="AD25" s="42"/>
-      <c r="AE25" s="42"/>
-      <c r="AF25" s="42"/>
-      <c r="AG25" s="42"/>
-      <c r="AH25" s="42"/>
-      <c r="AI25" s="42"/>
-      <c r="AJ25" s="42"/>
-      <c r="AK25" s="42"/>
-      <c r="AL25" s="43"/>
+      <c r="U25" s="53"/>
+      <c r="V25" s="53"/>
+      <c r="W25" s="53"/>
+      <c r="X25" s="53"/>
+      <c r="Y25" s="53"/>
+      <c r="Z25" s="53"/>
+      <c r="AA25" s="53"/>
+      <c r="AB25" s="53"/>
+      <c r="AC25" s="53"/>
+      <c r="AD25" s="53"/>
+      <c r="AE25" s="53"/>
+      <c r="AF25" s="53"/>
+      <c r="AG25" s="53"/>
+      <c r="AH25" s="53"/>
+      <c r="AI25" s="53"/>
+      <c r="AJ25" s="53"/>
+      <c r="AK25" s="53"/>
+      <c r="AL25" s="54"/>
       <c r="AM25" s="15"/>
     </row>
-    <row r="26" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="41" t="s">
+    <row r="26" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="42"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="41" t="s">
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="54"/>
+      <c r="T26" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="U26" s="42"/>
-      <c r="V26" s="42"/>
-      <c r="W26" s="42"/>
-      <c r="X26" s="42"/>
-      <c r="Y26" s="42"/>
-      <c r="Z26" s="42"/>
-      <c r="AA26" s="42"/>
-      <c r="AB26" s="42"/>
-      <c r="AC26" s="42"/>
-      <c r="AD26" s="42"/>
-      <c r="AE26" s="42"/>
-      <c r="AF26" s="42"/>
-      <c r="AG26" s="42"/>
-      <c r="AH26" s="42"/>
-      <c r="AI26" s="42"/>
-      <c r="AJ26" s="42"/>
-      <c r="AK26" s="42"/>
-      <c r="AL26" s="43"/>
+      <c r="U26" s="53"/>
+      <c r="V26" s="53"/>
+      <c r="W26" s="53"/>
+      <c r="X26" s="53"/>
+      <c r="Y26" s="53"/>
+      <c r="Z26" s="53"/>
+      <c r="AA26" s="53"/>
+      <c r="AB26" s="53"/>
+      <c r="AC26" s="53"/>
+      <c r="AD26" s="53"/>
+      <c r="AE26" s="53"/>
+      <c r="AF26" s="53"/>
+      <c r="AG26" s="53"/>
+      <c r="AH26" s="53"/>
+      <c r="AI26" s="53"/>
+      <c r="AJ26" s="53"/>
+      <c r="AK26" s="53"/>
+      <c r="AL26" s="54"/>
       <c r="AM26" s="15"/>
     </row>
-    <row r="27" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="59" t="s">
+    <row r="27" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="44" t="s">
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="M27" s="44"/>
-      <c r="N27" s="44"/>
-      <c r="O27" s="44"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="44"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="59" t="s">
+      <c r="M27" s="50"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="51"/>
+      <c r="T27" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="U27" s="60"/>
-      <c r="V27" s="60"/>
-      <c r="W27" s="60"/>
-      <c r="X27" s="60"/>
-      <c r="Y27" s="60"/>
-      <c r="Z27" s="60"/>
-      <c r="AA27" s="60"/>
-      <c r="AB27" s="60"/>
-      <c r="AC27" s="60"/>
-      <c r="AD27" s="60"/>
-      <c r="AE27" s="44" t="s">
+      <c r="U27" s="49"/>
+      <c r="V27" s="49"/>
+      <c r="W27" s="49"/>
+      <c r="X27" s="49"/>
+      <c r="Y27" s="49"/>
+      <c r="Z27" s="49"/>
+      <c r="AA27" s="49"/>
+      <c r="AB27" s="49"/>
+      <c r="AC27" s="49"/>
+      <c r="AD27" s="49"/>
+      <c r="AE27" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="AF27" s="44"/>
-      <c r="AG27" s="44"/>
-      <c r="AH27" s="44"/>
-      <c r="AI27" s="44"/>
-      <c r="AJ27" s="44"/>
-      <c r="AK27" s="44"/>
-      <c r="AL27" s="45"/>
+      <c r="AF27" s="50"/>
+      <c r="AG27" s="50"/>
+      <c r="AH27" s="50"/>
+      <c r="AI27" s="50"/>
+      <c r="AJ27" s="50"/>
+      <c r="AK27" s="50"/>
+      <c r="AL27" s="51"/>
       <c r="AM27" s="15"/>
     </row>
-    <row r="28" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="59" t="s">
+    <row r="28" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="60"/>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="60"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="60"/>
-      <c r="J28" s="60"/>
-      <c r="K28" s="60"/>
-      <c r="L28" s="44" t="s">
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="M28" s="44"/>
-      <c r="N28" s="44"/>
-      <c r="O28" s="44"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="59" t="s">
+      <c r="M28" s="50"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="50"/>
+      <c r="P28" s="50"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50"/>
+      <c r="S28" s="51"/>
+      <c r="T28" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="U28" s="60"/>
-      <c r="V28" s="60"/>
-      <c r="W28" s="60"/>
-      <c r="X28" s="60"/>
-      <c r="Y28" s="60"/>
-      <c r="Z28" s="60"/>
-      <c r="AA28" s="60"/>
-      <c r="AB28" s="60"/>
-      <c r="AC28" s="60"/>
-      <c r="AD28" s="60"/>
-      <c r="AE28" s="44" t="s">
+      <c r="U28" s="49"/>
+      <c r="V28" s="49"/>
+      <c r="W28" s="49"/>
+      <c r="X28" s="49"/>
+      <c r="Y28" s="49"/>
+      <c r="Z28" s="49"/>
+      <c r="AA28" s="49"/>
+      <c r="AB28" s="49"/>
+      <c r="AC28" s="49"/>
+      <c r="AD28" s="49"/>
+      <c r="AE28" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="AF28" s="44"/>
-      <c r="AG28" s="44"/>
-      <c r="AH28" s="44"/>
-      <c r="AI28" s="44"/>
-      <c r="AJ28" s="44"/>
-      <c r="AK28" s="44"/>
-      <c r="AL28" s="45"/>
+      <c r="AF28" s="50"/>
+      <c r="AG28" s="50"/>
+      <c r="AH28" s="50"/>
+      <c r="AI28" s="50"/>
+      <c r="AJ28" s="50"/>
+      <c r="AK28" s="50"/>
+      <c r="AL28" s="51"/>
       <c r="AM28" s="15"/>
     </row>
-    <row r="29" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="59" t="s">
+    <row r="29" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="60"/>
-      <c r="C29" s="60"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="60"/>
-      <c r="J29" s="60"/>
-      <c r="K29" s="60"/>
-      <c r="L29" s="44" t="s">
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="M29" s="44"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="44"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="44"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="59" t="s">
+      <c r="M29" s="50"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50"/>
+      <c r="S29" s="51"/>
+      <c r="T29" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="U29" s="60"/>
-      <c r="V29" s="60"/>
-      <c r="W29" s="60"/>
-      <c r="X29" s="60"/>
-      <c r="Y29" s="60"/>
-      <c r="Z29" s="60"/>
-      <c r="AA29" s="60"/>
-      <c r="AB29" s="60"/>
-      <c r="AC29" s="60"/>
-      <c r="AD29" s="60"/>
-      <c r="AE29" s="44" t="s">
+      <c r="U29" s="49"/>
+      <c r="V29" s="49"/>
+      <c r="W29" s="49"/>
+      <c r="X29" s="49"/>
+      <c r="Y29" s="49"/>
+      <c r="Z29" s="49"/>
+      <c r="AA29" s="49"/>
+      <c r="AB29" s="49"/>
+      <c r="AC29" s="49"/>
+      <c r="AD29" s="49"/>
+      <c r="AE29" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="AF29" s="44"/>
-      <c r="AG29" s="44"/>
-      <c r="AH29" s="44"/>
-      <c r="AI29" s="44"/>
-      <c r="AJ29" s="44"/>
-      <c r="AK29" s="44"/>
-      <c r="AL29" s="45"/>
+      <c r="AF29" s="50"/>
+      <c r="AG29" s="50"/>
+      <c r="AH29" s="50"/>
+      <c r="AI29" s="50"/>
+      <c r="AJ29" s="50"/>
+      <c r="AK29" s="50"/>
+      <c r="AL29" s="51"/>
       <c r="AM29" s="15"/>
     </row>
-    <row r="30" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="59" t="s">
+    <row r="30" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="60"/>
-      <c r="C30" s="60"/>
-      <c r="D30" s="60"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="60"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="60"/>
-      <c r="K30" s="60"/>
-      <c r="L30" s="44" t="s">
+      <c r="B30" s="49"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="49"/>
+      <c r="L30" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="M30" s="44"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="44"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="44"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="59" t="s">
+      <c r="M30" s="50"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="50"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50"/>
+      <c r="S30" s="51"/>
+      <c r="T30" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="U30" s="60"/>
-      <c r="V30" s="60"/>
-      <c r="W30" s="60"/>
-      <c r="X30" s="60"/>
-      <c r="Y30" s="60"/>
-      <c r="Z30" s="60"/>
-      <c r="AA30" s="60"/>
-      <c r="AB30" s="60"/>
-      <c r="AC30" s="60"/>
-      <c r="AD30" s="60"/>
-      <c r="AE30" s="44" t="s">
+      <c r="U30" s="49"/>
+      <c r="V30" s="49"/>
+      <c r="W30" s="49"/>
+      <c r="X30" s="49"/>
+      <c r="Y30" s="49"/>
+      <c r="Z30" s="49"/>
+      <c r="AA30" s="49"/>
+      <c r="AB30" s="49"/>
+      <c r="AC30" s="49"/>
+      <c r="AD30" s="49"/>
+      <c r="AE30" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="AF30" s="44"/>
-      <c r="AG30" s="44"/>
-      <c r="AH30" s="44"/>
-      <c r="AI30" s="44"/>
-      <c r="AJ30" s="44"/>
-      <c r="AK30" s="44"/>
-      <c r="AL30" s="45"/>
+      <c r="AF30" s="50"/>
+      <c r="AG30" s="50"/>
+      <c r="AH30" s="50"/>
+      <c r="AI30" s="50"/>
+      <c r="AJ30" s="50"/>
+      <c r="AK30" s="50"/>
+      <c r="AL30" s="51"/>
       <c r="AM30" s="15"/>
     </row>
-    <row r="31" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="59" t="s">
+    <row r="31" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="60"/>
-      <c r="K31" s="60"/>
-      <c r="L31" s="44" t="s">
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49"/>
+      <c r="L31" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="M31" s="44"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="44"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="59" t="s">
+      <c r="M31" s="50"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="51"/>
+      <c r="T31" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="U31" s="60"/>
-      <c r="V31" s="60"/>
-      <c r="W31" s="60"/>
-      <c r="X31" s="60"/>
-      <c r="Y31" s="60"/>
-      <c r="Z31" s="60"/>
-      <c r="AA31" s="60"/>
-      <c r="AB31" s="60"/>
-      <c r="AC31" s="60"/>
-      <c r="AD31" s="60"/>
-      <c r="AE31" s="44" t="s">
+      <c r="U31" s="49"/>
+      <c r="V31" s="49"/>
+      <c r="W31" s="49"/>
+      <c r="X31" s="49"/>
+      <c r="Y31" s="49"/>
+      <c r="Z31" s="49"/>
+      <c r="AA31" s="49"/>
+      <c r="AB31" s="49"/>
+      <c r="AC31" s="49"/>
+      <c r="AD31" s="49"/>
+      <c r="AE31" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="AF31" s="44"/>
-      <c r="AG31" s="44"/>
-      <c r="AH31" s="44"/>
-      <c r="AI31" s="44"/>
-      <c r="AJ31" s="44"/>
-      <c r="AK31" s="44"/>
-      <c r="AL31" s="45"/>
+      <c r="AF31" s="50"/>
+      <c r="AG31" s="50"/>
+      <c r="AH31" s="50"/>
+      <c r="AI31" s="50"/>
+      <c r="AJ31" s="50"/>
+      <c r="AK31" s="50"/>
+      <c r="AL31" s="51"/>
       <c r="AM31" s="15"/>
     </row>
-    <row r="32" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="41" t="s">
+    <row r="32" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="42"/>
-      <c r="S32" s="43"/>
-      <c r="T32" s="41" t="s">
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="53"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="53"/>
+      <c r="P32" s="53"/>
+      <c r="Q32" s="53"/>
+      <c r="R32" s="53"/>
+      <c r="S32" s="54"/>
+      <c r="T32" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="U32" s="42"/>
-      <c r="V32" s="42"/>
-      <c r="W32" s="42"/>
-      <c r="X32" s="42"/>
-      <c r="Y32" s="42"/>
-      <c r="Z32" s="42"/>
-      <c r="AA32" s="42"/>
-      <c r="AB32" s="42"/>
-      <c r="AC32" s="42"/>
-      <c r="AD32" s="42"/>
-      <c r="AE32" s="42"/>
-      <c r="AF32" s="42"/>
-      <c r="AG32" s="42"/>
-      <c r="AH32" s="42"/>
-      <c r="AI32" s="42"/>
-      <c r="AJ32" s="42"/>
-      <c r="AK32" s="42"/>
-      <c r="AL32" s="43"/>
+      <c r="U32" s="53"/>
+      <c r="V32" s="53"/>
+      <c r="W32" s="53"/>
+      <c r="X32" s="53"/>
+      <c r="Y32" s="53"/>
+      <c r="Z32" s="53"/>
+      <c r="AA32" s="53"/>
+      <c r="AB32" s="53"/>
+      <c r="AC32" s="53"/>
+      <c r="AD32" s="53"/>
+      <c r="AE32" s="53"/>
+      <c r="AF32" s="53"/>
+      <c r="AG32" s="53"/>
+      <c r="AH32" s="53"/>
+      <c r="AI32" s="53"/>
+      <c r="AJ32" s="53"/>
+      <c r="AK32" s="53"/>
+      <c r="AL32" s="54"/>
       <c r="AM32" s="15"/>
     </row>
-    <row r="33" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="46" t="s">
+    <row r="33" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="47"/>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="47"/>
-      <c r="O33" s="47"/>
-      <c r="P33" s="47"/>
-      <c r="Q33" s="47"/>
-      <c r="R33" s="47"/>
-      <c r="S33" s="48"/>
-      <c r="T33" s="46" t="s">
+      <c r="B33" s="42"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="42"/>
+      <c r="S33" s="43"/>
+      <c r="T33" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="U33" s="47"/>
-      <c r="V33" s="47"/>
-      <c r="W33" s="47"/>
-      <c r="X33" s="47"/>
-      <c r="Y33" s="47"/>
-      <c r="Z33" s="47"/>
-      <c r="AA33" s="47"/>
-      <c r="AB33" s="47"/>
-      <c r="AC33" s="47"/>
-      <c r="AD33" s="47"/>
-      <c r="AE33" s="47"/>
-      <c r="AF33" s="47"/>
-      <c r="AG33" s="47"/>
-      <c r="AH33" s="47"/>
-      <c r="AI33" s="47"/>
-      <c r="AJ33" s="47"/>
-      <c r="AK33" s="47"/>
-      <c r="AL33" s="48"/>
+      <c r="U33" s="42"/>
+      <c r="V33" s="42"/>
+      <c r="W33" s="42"/>
+      <c r="X33" s="42"/>
+      <c r="Y33" s="42"/>
+      <c r="Z33" s="42"/>
+      <c r="AA33" s="42"/>
+      <c r="AB33" s="42"/>
+      <c r="AC33" s="42"/>
+      <c r="AD33" s="42"/>
+      <c r="AE33" s="42"/>
+      <c r="AF33" s="42"/>
+      <c r="AG33" s="42"/>
+      <c r="AH33" s="42"/>
+      <c r="AI33" s="42"/>
+      <c r="AJ33" s="42"/>
+      <c r="AK33" s="42"/>
+      <c r="AL33" s="43"/>
       <c r="AM33" s="15"/>
     </row>
-    <row r="34" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="49"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="47"/>
-      <c r="P34" s="47"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47"/>
-      <c r="S34" s="48"/>
-      <c r="T34" s="49"/>
-      <c r="U34" s="47"/>
-      <c r="V34" s="47"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="47"/>
-      <c r="Y34" s="47"/>
-      <c r="Z34" s="47"/>
-      <c r="AA34" s="47"/>
-      <c r="AB34" s="47"/>
-      <c r="AC34" s="47"/>
-      <c r="AD34" s="47"/>
-      <c r="AE34" s="47"/>
-      <c r="AF34" s="47"/>
-      <c r="AG34" s="47"/>
-      <c r="AH34" s="47"/>
-      <c r="AI34" s="47"/>
-      <c r="AJ34" s="47"/>
-      <c r="AK34" s="47"/>
-      <c r="AL34" s="48"/>
+    <row r="34" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="44"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="42"/>
+      <c r="S34" s="43"/>
+      <c r="T34" s="44"/>
+      <c r="U34" s="42"/>
+      <c r="V34" s="42"/>
+      <c r="W34" s="42"/>
+      <c r="X34" s="42"/>
+      <c r="Y34" s="42"/>
+      <c r="Z34" s="42"/>
+      <c r="AA34" s="42"/>
+      <c r="AB34" s="42"/>
+      <c r="AC34" s="42"/>
+      <c r="AD34" s="42"/>
+      <c r="AE34" s="42"/>
+      <c r="AF34" s="42"/>
+      <c r="AG34" s="42"/>
+      <c r="AH34" s="42"/>
+      <c r="AI34" s="42"/>
+      <c r="AJ34" s="42"/>
+      <c r="AK34" s="42"/>
+      <c r="AL34" s="43"/>
       <c r="AM34" s="15"/>
     </row>
-    <row r="35" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="49"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="48"/>
-      <c r="T35" s="49"/>
-      <c r="U35" s="47"/>
-      <c r="V35" s="47"/>
-      <c r="W35" s="47"/>
-      <c r="X35" s="47"/>
-      <c r="Y35" s="47"/>
-      <c r="Z35" s="47"/>
-      <c r="AA35" s="47"/>
-      <c r="AB35" s="47"/>
-      <c r="AC35" s="47"/>
-      <c r="AD35" s="47"/>
-      <c r="AE35" s="47"/>
-      <c r="AF35" s="47"/>
-      <c r="AG35" s="47"/>
-      <c r="AH35" s="47"/>
-      <c r="AI35" s="47"/>
-      <c r="AJ35" s="47"/>
-      <c r="AK35" s="47"/>
-      <c r="AL35" s="48"/>
+    <row r="35" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="44"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="42"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="42"/>
+      <c r="N35" s="42"/>
+      <c r="O35" s="42"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="42"/>
+      <c r="S35" s="43"/>
+      <c r="T35" s="44"/>
+      <c r="U35" s="42"/>
+      <c r="V35" s="42"/>
+      <c r="W35" s="42"/>
+      <c r="X35" s="42"/>
+      <c r="Y35" s="42"/>
+      <c r="Z35" s="42"/>
+      <c r="AA35" s="42"/>
+      <c r="AB35" s="42"/>
+      <c r="AC35" s="42"/>
+      <c r="AD35" s="42"/>
+      <c r="AE35" s="42"/>
+      <c r="AF35" s="42"/>
+      <c r="AG35" s="42"/>
+      <c r="AH35" s="42"/>
+      <c r="AI35" s="42"/>
+      <c r="AJ35" s="42"/>
+      <c r="AK35" s="42"/>
+      <c r="AL35" s="43"/>
       <c r="AM35" s="15"/>
     </row>
-    <row r="36" spans="1:39" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="50"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
-      <c r="K36" s="51"/>
-      <c r="L36" s="51"/>
-      <c r="M36" s="51"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="51"/>
-      <c r="Q36" s="51"/>
-      <c r="R36" s="51"/>
-      <c r="S36" s="52"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="51"/>
-      <c r="V36" s="51"/>
-      <c r="W36" s="51"/>
-      <c r="X36" s="51"/>
-      <c r="Y36" s="51"/>
-      <c r="Z36" s="51"/>
-      <c r="AA36" s="51"/>
-      <c r="AB36" s="51"/>
-      <c r="AC36" s="51"/>
-      <c r="AD36" s="51"/>
-      <c r="AE36" s="51"/>
-      <c r="AF36" s="51"/>
-      <c r="AG36" s="51"/>
-      <c r="AH36" s="51"/>
-      <c r="AI36" s="51"/>
-      <c r="AJ36" s="51"/>
-      <c r="AK36" s="51"/>
-      <c r="AL36" s="52"/>
+    <row r="36" spans="1:39" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="45"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="46"/>
+      <c r="P36" s="46"/>
+      <c r="Q36" s="46"/>
+      <c r="R36" s="46"/>
+      <c r="S36" s="47"/>
+      <c r="T36" s="45"/>
+      <c r="U36" s="46"/>
+      <c r="V36" s="46"/>
+      <c r="W36" s="46"/>
+      <c r="X36" s="46"/>
+      <c r="Y36" s="46"/>
+      <c r="Z36" s="46"/>
+      <c r="AA36" s="46"/>
+      <c r="AB36" s="46"/>
+      <c r="AC36" s="46"/>
+      <c r="AD36" s="46"/>
+      <c r="AE36" s="46"/>
+      <c r="AF36" s="46"/>
+      <c r="AG36" s="46"/>
+      <c r="AH36" s="46"/>
+      <c r="AI36" s="46"/>
+      <c r="AJ36" s="46"/>
+      <c r="AK36" s="46"/>
+      <c r="AL36" s="47"/>
       <c r="AM36" s="15"/>
     </row>
-    <row r="37" spans="1:39" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="53" t="s">
+    <row r="37" spans="1:39" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="54"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="54"/>
-      <c r="I37" s="54"/>
-      <c r="J37" s="54"/>
-      <c r="K37" s="54"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="54"/>
-      <c r="N37" s="54"/>
-      <c r="O37" s="54"/>
-      <c r="P37" s="54"/>
-      <c r="Q37" s="54"/>
-      <c r="R37" s="54"/>
-      <c r="S37" s="54"/>
-      <c r="T37" s="54"/>
-      <c r="U37" s="54"/>
-      <c r="V37" s="54"/>
-      <c r="W37" s="54"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="54"/>
-      <c r="Z37" s="54"/>
-      <c r="AA37" s="54"/>
-      <c r="AB37" s="54"/>
-      <c r="AC37" s="54"/>
-      <c r="AD37" s="54"/>
-      <c r="AE37" s="54"/>
-      <c r="AF37" s="54"/>
-      <c r="AG37" s="54"/>
-      <c r="AH37" s="54"/>
-      <c r="AI37" s="54"/>
-      <c r="AJ37" s="54"/>
-      <c r="AK37" s="54"/>
-      <c r="AL37" s="55"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="67"/>
+      <c r="K37" s="67"/>
+      <c r="L37" s="67"/>
+      <c r="M37" s="67"/>
+      <c r="N37" s="67"/>
+      <c r="O37" s="67"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="67"/>
+      <c r="S37" s="67"/>
+      <c r="T37" s="67"/>
+      <c r="U37" s="67"/>
+      <c r="V37" s="67"/>
+      <c r="W37" s="67"/>
+      <c r="X37" s="67"/>
+      <c r="Y37" s="67"/>
+      <c r="Z37" s="67"/>
+      <c r="AA37" s="67"/>
+      <c r="AB37" s="67"/>
+      <c r="AC37" s="67"/>
+      <c r="AD37" s="67"/>
+      <c r="AE37" s="67"/>
+      <c r="AF37" s="67"/>
+      <c r="AG37" s="67"/>
+      <c r="AH37" s="67"/>
+      <c r="AI37" s="67"/>
+      <c r="AJ37" s="67"/>
+      <c r="AK37" s="67"/>
+      <c r="AL37" s="68"/>
       <c r="AM37" s="15"/>
     </row>
-    <row r="38" spans="1:39" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="56"/>
-      <c r="B38" s="57"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="57"/>
-      <c r="L38" s="57"/>
-      <c r="M38" s="57"/>
-      <c r="N38" s="57"/>
-      <c r="O38" s="57"/>
-      <c r="P38" s="57"/>
-      <c r="Q38" s="57"/>
-      <c r="R38" s="57"/>
-      <c r="S38" s="57"/>
-      <c r="T38" s="57"/>
-      <c r="U38" s="57"/>
-      <c r="V38" s="57"/>
-      <c r="W38" s="57"/>
-      <c r="X38" s="57"/>
-      <c r="Y38" s="57"/>
-      <c r="Z38" s="57"/>
-      <c r="AA38" s="57"/>
-      <c r="AB38" s="57"/>
-      <c r="AC38" s="57"/>
-      <c r="AD38" s="57"/>
-      <c r="AE38" s="57"/>
-      <c r="AF38" s="57"/>
-      <c r="AG38" s="57"/>
-      <c r="AH38" s="57"/>
-      <c r="AI38" s="57"/>
-      <c r="AJ38" s="57"/>
-      <c r="AK38" s="57"/>
-      <c r="AL38" s="58"/>
+    <row r="38" spans="1:39" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="69"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
+      <c r="S38" s="70"/>
+      <c r="T38" s="70"/>
+      <c r="U38" s="70"/>
+      <c r="V38" s="70"/>
+      <c r="W38" s="70"/>
+      <c r="X38" s="70"/>
+      <c r="Y38" s="70"/>
+      <c r="Z38" s="70"/>
+      <c r="AA38" s="70"/>
+      <c r="AB38" s="70"/>
+      <c r="AC38" s="70"/>
+      <c r="AD38" s="70"/>
+      <c r="AE38" s="70"/>
+      <c r="AF38" s="70"/>
+      <c r="AG38" s="70"/>
+      <c r="AH38" s="70"/>
+      <c r="AI38" s="70"/>
+      <c r="AJ38" s="70"/>
+      <c r="AK38" s="70"/>
+      <c r="AL38" s="71"/>
       <c r="AM38" s="15"/>
     </row>
-    <row r="39" spans="1:39" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A39" s="28" t="s">
         <v>3</v>
       </c>
@@ -3547,7 +3547,7 @@
       <c r="AL39" s="16"/>
       <c r="AM39" s="15"/>
     </row>
-    <row r="40" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="32" t="s">
         <v>57</v>
       </c>
@@ -3590,7 +3590,7 @@
       <c r="AL40" s="16"/>
       <c r="AM40" s="15"/>
     </row>
-    <row r="41" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="14"/>
       <c r="D41" s="28" t="s">
         <v>56</v>
@@ -3631,7 +3631,7 @@
       <c r="AL41" s="16"/>
       <c r="AM41" s="15"/>
     </row>
-    <row r="42" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="28" t="s">
         <v>59</v>
       </c>
@@ -3674,7 +3674,7 @@
       <c r="AL42" s="16"/>
       <c r="AM42" s="15"/>
     </row>
-    <row r="43" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="14"/>
       <c r="D43" s="28" t="s">
         <v>60</v>
@@ -3715,7 +3715,7 @@
       <c r="AL43" s="16"/>
       <c r="AM43" s="15"/>
     </row>
-    <row r="44" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
         <v>61</v>
       </c>
@@ -3758,7 +3758,7 @@
       <c r="AL44" s="16"/>
       <c r="AM44" s="15"/>
     </row>
-    <row r="45" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="14"/>
       <c r="D45" s="28" t="s">
         <v>64</v>
@@ -3799,7 +3799,7 @@
       <c r="AL45" s="16"/>
       <c r="AM45" s="15"/>
     </row>
-    <row r="46" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="32" t="s">
         <v>65</v>
       </c>
@@ -3839,7 +3839,7 @@
       <c r="AL46" s="16"/>
       <c r="AM46" s="15"/>
     </row>
-    <row r="47" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="32" t="s">
         <v>66</v>
       </c>
@@ -3879,7 +3879,7 @@
       <c r="AL47" s="16"/>
       <c r="AM47" s="15"/>
     </row>
-    <row r="48" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="36" t="s">
         <v>67</v>
       </c>
@@ -3919,7 +3919,7 @@
       <c r="AL48" s="16"/>
       <c r="AM48" s="15"/>
     </row>
-    <row r="49" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="32" t="s">
         <v>68</v>
       </c>
@@ -3959,7 +3959,7 @@
       <c r="AL49" s="16"/>
       <c r="AM49" s="15"/>
     </row>
-    <row r="50" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="32" t="s">
         <v>69</v>
       </c>
@@ -3999,7 +3999,7 @@
       <c r="AL50" s="16"/>
       <c r="AM50" s="15"/>
     </row>
-    <row r="51" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="32" t="s">
         <v>70</v>
       </c>
@@ -4039,7 +4039,7 @@
       <c r="AL51" s="16"/>
       <c r="AM51" s="15"/>
     </row>
-    <row r="52" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="32" t="s">
         <v>71</v>
       </c>
@@ -4079,7 +4079,7 @@
       <c r="AL52" s="16"/>
       <c r="AM52" s="15"/>
     </row>
-    <row r="53" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="32" t="s">
         <v>72</v>
       </c>
@@ -4119,7 +4119,7 @@
       <c r="AL53" s="16"/>
       <c r="AM53" s="15"/>
     </row>
-    <row r="54" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="32" t="s">
         <v>73</v>
       </c>
@@ -4159,7 +4159,7 @@
       <c r="AL54" s="16"/>
       <c r="AM54" s="15"/>
     </row>
-    <row r="55" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="32" t="s">
         <v>74</v>
       </c>
@@ -4199,7 +4199,7 @@
       <c r="AL55" s="16"/>
       <c r="AM55" s="15"/>
     </row>
-    <row r="56" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="18" t="s">
         <v>2</v>
       </c>
@@ -4239,7 +4239,7 @@
       <c r="AL56" s="16"/>
       <c r="AM56" s="15"/>
     </row>
-    <row r="57" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -4277,7 +4277,7 @@
       <c r="AL57" s="16"/>
       <c r="AM57" s="15"/>
     </row>
-    <row r="58" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
@@ -4315,7 +4315,7 @@
       <c r="AL58" s="16"/>
       <c r="AM58" s="15"/>
     </row>
-    <row r="59" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -4353,7 +4353,7 @@
       <c r="AL59" s="16"/>
       <c r="AM59" s="15"/>
     </row>
-    <row r="60" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="12"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -4384,7 +4384,7 @@
       <c r="AE60" s="1"/>
       <c r="AF60" s="1"/>
     </row>
-    <row r="61" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="13"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -4415,7 +4415,7 @@
       <c r="AE61" s="1"/>
       <c r="AF61" s="1"/>
     </row>
-    <row r="62" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="12"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
@@ -4446,7 +4446,7 @@
       <c r="AE62" s="1"/>
       <c r="AF62" s="1"/>
     </row>
-    <row r="63" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="7"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
@@ -4487,7 +4487,7 @@
       <c r="AL63" s="9"/>
       <c r="AM63" s="9"/>
     </row>
-    <row r="64" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="7"/>
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
@@ -4528,7 +4528,7 @@
       <c r="AL64" s="9"/>
       <c r="AM64" s="9"/>
     </row>
-    <row r="65" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="9"/>
       <c r="C65" s="9"/>
@@ -4569,7 +4569,7 @@
       <c r="AL65" s="9"/>
       <c r="AM65" s="9"/>
     </row>
-    <row r="66" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -4610,8 +4610,8 @@
       <c r="AL66" s="4"/>
       <c r="AM66" s="4"/>
     </row>
-    <row r="67" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="6"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -4627,7 +4627,7 @@
       <c r="M68" s="8"/>
       <c r="N68" s="8"/>
     </row>
-    <row r="69" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -4643,7 +4643,7 @@
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
     </row>
-    <row r="70" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A70" s="6"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -4661,6 +4661,51 @@
     </row>
   </sheetData>
   <mergeCells count="61">
+    <mergeCell ref="A32:S32"/>
+    <mergeCell ref="AE28:AL28"/>
+    <mergeCell ref="T32:AL32"/>
+    <mergeCell ref="T33:AL36"/>
+    <mergeCell ref="A37:AL38"/>
+    <mergeCell ref="T29:AD29"/>
+    <mergeCell ref="AE29:AL29"/>
+    <mergeCell ref="T30:AD30"/>
+    <mergeCell ref="AE30:AL30"/>
+    <mergeCell ref="T31:AD31"/>
+    <mergeCell ref="AE31:AL31"/>
+    <mergeCell ref="L29:S29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="L30:S30"/>
+    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="L31:S31"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="L28:S28"/>
+    <mergeCell ref="T20:AD20"/>
+    <mergeCell ref="AE20:AL20"/>
+    <mergeCell ref="T21:AD21"/>
+    <mergeCell ref="AE21:AL21"/>
+    <mergeCell ref="T22:AD22"/>
+    <mergeCell ref="AE22:AL22"/>
+    <mergeCell ref="T23:AD23"/>
+    <mergeCell ref="AE23:AL23"/>
+    <mergeCell ref="T24:AD24"/>
+    <mergeCell ref="AE24:AL24"/>
+    <mergeCell ref="T25:AL25"/>
+    <mergeCell ref="T26:AL26"/>
+    <mergeCell ref="T27:AD27"/>
+    <mergeCell ref="AE27:AL27"/>
+    <mergeCell ref="T28:AD28"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A13:S16"/>
+    <mergeCell ref="T13:AL16"/>
+    <mergeCell ref="A17:K19"/>
+    <mergeCell ref="L17:S19"/>
+    <mergeCell ref="T17:AD19"/>
+    <mergeCell ref="AE17:AL19"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A12:S12"/>
+    <mergeCell ref="T12:AL12"/>
+    <mergeCell ref="A4:AL5"/>
     <mergeCell ref="A33:S36"/>
     <mergeCell ref="A20:K20"/>
     <mergeCell ref="A21:K21"/>
@@ -4677,51 +4722,6 @@
     <mergeCell ref="A27:K27"/>
     <mergeCell ref="L27:S27"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="T28:AD28"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A13:S16"/>
-    <mergeCell ref="T13:AL16"/>
-    <mergeCell ref="A17:K19"/>
-    <mergeCell ref="L17:S19"/>
-    <mergeCell ref="T17:AD19"/>
-    <mergeCell ref="AE17:AL19"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:AM5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A12:S12"/>
-    <mergeCell ref="T12:AL12"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="L28:S28"/>
-    <mergeCell ref="T20:AD20"/>
-    <mergeCell ref="AE20:AL20"/>
-    <mergeCell ref="T21:AD21"/>
-    <mergeCell ref="AE21:AL21"/>
-    <mergeCell ref="T22:AD22"/>
-    <mergeCell ref="AE22:AL22"/>
-    <mergeCell ref="T23:AD23"/>
-    <mergeCell ref="AE23:AL23"/>
-    <mergeCell ref="T24:AD24"/>
-    <mergeCell ref="AE24:AL24"/>
-    <mergeCell ref="T25:AL25"/>
-    <mergeCell ref="T26:AL26"/>
-    <mergeCell ref="T27:AD27"/>
-    <mergeCell ref="AE27:AL27"/>
-    <mergeCell ref="A32:S32"/>
-    <mergeCell ref="AE28:AL28"/>
-    <mergeCell ref="T32:AL32"/>
-    <mergeCell ref="T33:AL36"/>
-    <mergeCell ref="A37:AL38"/>
-    <mergeCell ref="T29:AD29"/>
-    <mergeCell ref="AE29:AL29"/>
-    <mergeCell ref="T30:AD30"/>
-    <mergeCell ref="AE30:AL30"/>
-    <mergeCell ref="T31:AD31"/>
-    <mergeCell ref="AE31:AL31"/>
-    <mergeCell ref="L29:S29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="L30:S30"/>
-    <mergeCell ref="A31:K31"/>
-    <mergeCell ref="L31:S31"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
